--- a/Employee_Reports_wi52/Jake Alinabon Salibay Q0554.xlsx
+++ b/Employee_Reports_wi52/Jake Alinabon Salibay Q0554.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +93,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +475,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -569,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-96</v>
+        <v>-104</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-27</v>
+        <v>-35</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-90</v>
+        <v>-98</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-71</v>
+        <v>-79</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-92</v>
+        <v>-100</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-127</v>
+        <v>-135</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1206,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-317</v>
+        <v>-325</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1305,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-311</v>
+        <v>-319</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1354,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-680</v>
+        <v>-688</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1403,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-133</v>
+        <v>-141</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1452,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1501,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1550,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-33</v>
+        <v>-41</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1599,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1648,11 +1657,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1685,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-27</v>
+        <v>-35</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1700,41 +1709,41 @@
       <c r="K26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>30-Sep-2025</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1771,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1820,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
